--- a/www/download/IND.surplus_value.empe.r.pc.zdW16.xlsx
+++ b/www/download/IND.surplus_value.empe.r.pc.zdW16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>80.48</t>
+          <t>1.04753624091599</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>1.10311387569909</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>0.911325440002864</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>0.643737729719284</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>33.63</t>
+          <t>0.50516337328839</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>0.479894941306034</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>0.56405944532562</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>0.510489750209571</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>0.691339896947683</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>0.686124169405865</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>0.582964085817172</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>0.436215638848023</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>0.492012340395014</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>0.476025161700944</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>50.86</t>
+          <t>0.508629551044103</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>1.11197027942877</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>83.09</t>
+          <t>1.16510057149524</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>85.08</t>
+          <t>1.19094330470124</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>74.57</t>
+          <t>1.07050730376187</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>73.71</t>
+          <t>1.04695947287534</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>78.11</t>
+          <t>1.08971319175461</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>1.0238989079926</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>75.78</t>
+          <t>1.04699491294081</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>78.06</t>
+          <t>1.08228523060425</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>76.02</t>
+          <t>1.0866689297083</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>1.17175437795564</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>1.13974412126656</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>77.98</t>
+          <t>1.09185496102201</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>0.918203886178541</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>93.64</t>
+          <t>0.936394749865562</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-30.59</t>
+          <t>-0.213715471255739</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-31.34</t>
+          <t>-0.226651662849339</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.27</t>
+          <t>-0.257272067753261</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-41.9</t>
+          <t>-0.344724648932419</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-46.24</t>
+          <t>-0.397323744902328</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-43.97</t>
+          <t>-0.369002186307113</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-40.56</t>
+          <t>-0.32929720945302</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-38.58</t>
+          <t>-0.311307039188014</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-37.02</t>
+          <t>-0.290070324701573</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-32.43</t>
+          <t>-0.233974381477481</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-9.6</t>
+          <t>0.0294302752646813</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-10.8</t>
+          <t>0.0183592346428341</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>0.0797622460355429</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>0.00139609845219302</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-0.0462500531353179</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>197.71</t>
+          <t>2.40538801000808</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>202.97</t>
+          <t>2.45593536181026</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>209.69</t>
+          <t>2.52703277359167</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>215.37</t>
+          <t>2.59864177208506</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>234.91</t>
+          <t>2.77473505299425</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>250.52</t>
+          <t>2.97535255919608</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>247.04</t>
+          <t>2.94729104662314</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>279.11</t>
+          <t>3.28858870394017</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>290.37</t>
+          <t>3.41915361478291</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>2.95085158233221</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>268.15</t>
+          <t>3.19916048904528</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>283.46</t>
+          <t>3.36861636689874</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>267.26</t>
+          <t>3.19443013408028</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>252.91</t>
+          <t>3.02369144627335</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>261.83</t>
+          <t>2.61833512268199</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>311.95</t>
+          <t>3.57517070177479</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>345.87</t>
+          <t>3.97629522073411</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>349.69</t>
+          <t>4.04653330461551</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>365.05</t>
+          <t>4.23630315743094</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>372.73</t>
+          <t>4.28798753929746</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>359.19</t>
+          <t>4.15001850145347</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>359.76</t>
+          <t>4.13657102121472</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>369.38</t>
+          <t>4.21329042701988</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>343.01</t>
+          <t>3.9518544225876</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>316.59</t>
+          <t>3.70656442048501</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>305.4</t>
+          <t>3.57227693859088</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>311.39</t>
+          <t>3.63936028645562</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>313.36</t>
+          <t>3.67891293700738</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>329.32</t>
+          <t>3.84890236385224</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>380.52</t>
+          <t>3.80517762298943</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>72.19</t>
+          <t>0.915680128627046</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>71.04</t>
+          <t>0.891480826546932</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>0.81800821687967</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>53.91</t>
+          <t>0.704192498229699</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>0.627076557267673</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>0.586802412264607</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>40.41</t>
+          <t>0.564647045937654</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>0.641957405772211</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>57.73</t>
+          <t>0.762086479997353</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>0.765259081426376</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>63.69</t>
+          <t>0.839059338611021</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>54.18</t>
+          <t>0.737315152129592</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>0.757813165218328</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>0.776540712639902</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>87.43</t>
+          <t>0.874277421368411</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>0.0536704470912386</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.118532857439535</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0.156995154814429</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0.253716512145182</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>0.305874492651072</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>0.39486811963009</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>0.376034062673678</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>0.461361064525796</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>0.405478188308024</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>0.369591835308116</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>0.40023274832439</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>0.471671731557074</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>0.447231666100639</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>0.529795243741759</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>55.65</t>
+          <t>0.556460753391576</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>66.77</t>
+          <t>0.90665089907806</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>53.88</t>
+          <t>0.742674894043201</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>0.481466962495283</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>0.301033077305237</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.48</t>
+          <t>0.322237422751094</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>0.390748887162539</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>0.572148606082651</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>0.664452932870564</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>0.518863407865247</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>0.7383750522711</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>50.86</t>
+          <t>0.731238376535209</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>55.97</t>
+          <t>0.784240065201964</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>0.907414533300245</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>0.831177481322434</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>82.51</t>
+          <t>0.825069025001888</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>357.55</t>
+          <t>4.40681124721684</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>333.94</t>
+          <t>4.13715480827803</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>302.12</t>
+          <t>3.83094648054544</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>265.62</t>
+          <t>3.35613206775773</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>261.53</t>
+          <t>3.24372428626892</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>252.53</t>
+          <t>3.13084959301565</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>256.82</t>
+          <t>3.18937878365419</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>256.43</t>
+          <t>3.17177175940011</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>252.86</t>
+          <t>3.18502854390404</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>269.59</t>
+          <t>3.4535585731146</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>277.74</t>
+          <t>3.54875751732848</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>253.88</t>
+          <t>3.28152984079044</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>272.05</t>
+          <t>3.48812905093102</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>255.93</t>
+          <t>3.25643813188235</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>340.73</t>
+          <t>3.40725695651619</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>0.440983000790671</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.48069011083725</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>26.29</t>
+          <t>0.464716188019174</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>0.304506066210631</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>0.262585702719315</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>0.295273287242645</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>0.29546459385389</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>0.300788491472431</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>17.19</t>
+          <t>0.362977117659409</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>17.74</t>
+          <t>0.376331156230283</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>0.534139670594727</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>0.431021802531713</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>32.51</t>
+          <t>0.543153869799391</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>0.39376853176655</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>39.71</t>
+          <t>0.397125440290991</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>0.390701521901026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>0.363768471268401</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>0.357400978045456</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.147642458152364</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>0.164929777157885</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.156406828427689</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>0.208691209969827</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>0.249001470052009</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>0.247687224858809</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>0.307464491818963</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>0.363902087071997</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>0.406536530068828</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>0.502534007567777</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>0.703519415488193</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>61.25</t>
+          <t>0.612458254268609</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>88.72</t>
+          <t>1.11590983213153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>84.57</t>
+          <t>1.05710185585793</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.84</t>
+          <t>0.97229376827716</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>63.65</t>
+          <t>0.826059719302554</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>0.70584101615439</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>0.724441507642792</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>58.89</t>
+          <t>0.776032168782179</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>59.48</t>
+          <t>0.770116140303884</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>55.63</t>
+          <t>0.73335090119834</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>64.41</t>
+          <t>0.838595983809207</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>76.18</t>
+          <t>0.982190590042802</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>0.94736100932218</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>85.52</t>
+          <t>1.09666423577884</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>0.97227672020252</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>93.99</t>
+          <t>0.939857709593435</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>239.3</t>
+          <t>2.75384562006541</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>254.75</t>
+          <t>2.95335492298744</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>187.39</t>
+          <t>2.2055730959545</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>154.07</t>
+          <t>1.84687874160889</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>167.73</t>
+          <t>1.97748308297053</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>177.44</t>
+          <t>2.09531896954165</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>137.05</t>
+          <t>1.65460959974172</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>127.59</t>
+          <t>1.53514111022025</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>1.46946193075317</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>151.39</t>
+          <t>1.86265061021642</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>178.75</t>
+          <t>2.14683293663151</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>173.32</t>
+          <t>2.09635562558765</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>176.12</t>
+          <t>2.14577073404577</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>172.65</t>
+          <t>2.11752228471787</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>169.2</t>
+          <t>1.69204398988287</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>78.14</t>
+          <t>1.03500269948002</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>81.52</t>
+          <t>1.07598446760514</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>74.56</t>
+          <t>0.994077628000001</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>0.803958196397047</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>0.698930368293467</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>0.667730755252166</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>0.72709353453988</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>52.99</t>
+          <t>0.751293726919687</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>47.93</t>
+          <t>0.702919036298</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>60.98</t>
+          <t>0.863214612283786</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>78.81</t>
+          <t>1.05176895194027</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>86.32</t>
+          <t>1.14876501312253</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>77.01</t>
+          <t>1.04511173909528</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>72.21</t>
+          <t>0.973672271699856</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>107.08</t>
+          <t>1.07077695064112</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>0.434801482766006</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>0.407706112787998</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>0.287518763447468</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>0.176132511646567</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>0.197079319305291</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>0.208560194992566</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>0.23777681667141</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>0.279763764281905</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>0.322897292083599</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>0.407467253855339</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>0.588024782465945</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>0.496845044780329</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>0.581600251221084</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>33.68</t>
+          <t>0.511005905787629</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>0.454986773603329</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>0.53520327941791</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>0.436106284123531</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>0.35251946621683</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>0.317703416230855</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>0.208929565563563</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>0.237089345700159</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>0.220038261598006</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>0.313352688293955</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>31.73</t>
+          <t>0.48165931310174</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>0.602345063099274</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>0.790819255856505</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>62.77</t>
+          <t>0.852863696939429</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>0.8601660593141</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>0.61953809725743</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>99.05</t>
+          <t>0.990489146581464</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>126.74</t>
+          <t>1.48687030607271</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>134.24</t>
+          <t>1.57490597026782</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>124.35</t>
+          <t>1.4711952664668</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>107.39</t>
+          <t>1.27627151826504</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>104.37</t>
+          <t>1.23818437672431</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>98.92</t>
+          <t>1.18476029114247</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>94.67</t>
+          <t>1.13921800134124</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>95.41</t>
+          <t>1.14318203780552</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>97.95</t>
+          <t>1.18056996080379</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>99.12</t>
+          <t>1.19926647942597</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>117.71</t>
+          <t>1.41517219109821</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>115.57</t>
+          <t>1.39567282241095</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>145.67</t>
+          <t>1.72780908717317</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>150.52</t>
+          <t>1.78206318057438</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>169.13</t>
+          <t>1.6913344550924</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>252.17</t>
+          <t>3.21943149664011</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>243.62</t>
+          <t>3.1272574395235</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>223.22</t>
+          <t>2.86692449929854</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>209.6</t>
+          <t>2.7117331494476</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>234.63</t>
+          <t>3.0008354554525</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>255.98</t>
+          <t>3.26189363960057</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>272.64</t>
+          <t>3.43622938504031</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>288.35</t>
+          <t>3.66607260125169</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>293.97</t>
+          <t>3.73652919407477</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>303.4</t>
+          <t>3.91769502171528</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>321.12</t>
+          <t>4.1019553712032</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>322.05</t>
+          <t>4.05873502413434</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>342.69</t>
+          <t>4.31883970021373</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>343.44</t>
+          <t>4.3207294624258</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>406.75</t>
+          <t>4.06750912115808</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>140.94</t>
+          <t>1.49996622163533</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>143.97</t>
+          <t>1.52204266224094</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>151.09</t>
+          <t>1.60714485392519</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>114.81</t>
+          <t>1.23456124119818</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>123.59</t>
+          <t>1.33398056460257</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>108.14</t>
+          <t>1.17389465320344</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>106.53</t>
+          <t>1.22963026022162</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>100.12</t>
+          <t>1.16661701693575</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>106.77</t>
+          <t>1.24627010917811</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>95.76</t>
+          <t>1.12997961503323</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>106.73</t>
+          <t>1.24529070597207</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>112.11</t>
+          <t>1.30830775805036</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>119.62</t>
+          <t>1.38941064405552</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>126.81</t>
+          <t>1.45330965298808</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>146.13</t>
+          <t>1.4613062824333</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>134.92</t>
+          <t>1.46416019182185</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>140.39</t>
+          <t>1.51657324878588</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>143.56</t>
+          <t>1.54533666746637</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>145.55</t>
+          <t>1.56915378826044</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>153.89</t>
+          <t>1.64910062886592</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>157.51</t>
+          <t>1.68260362751999</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>166.97</t>
+          <t>1.7789848998784</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>169.09</t>
+          <t>1.81085010048908</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>180.15</t>
+          <t>1.92658140044398</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>182.37</t>
+          <t>1.96199574386592</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>189.02</t>
+          <t>2.03174005133574</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>183.42</t>
+          <t>1.97759443796576</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>193.08</t>
+          <t>2.10346763813356</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>200.23</t>
+          <t>2.17723380022653</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>223.88</t>
+          <t>2.23877724149117</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>124.05</t>
+          <t>1.49262360035441</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>1.09227799732407</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>0.985662726911818</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>79.87</t>
+          <t>1.01950232533894</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>57.17</t>
+          <t>0.753864325607498</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>50.34</t>
+          <t>0.686411909310829</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>0.674985961396734</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>53.04</t>
+          <t>0.711899623503027</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>51.93</t>
+          <t>0.706662573405148</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>79.28</t>
+          <t>1.05970067447723</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>176.98</t>
+          <t>2.18171697074198</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>97.63</t>
+          <t>1.27580267611396</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>110.63</t>
+          <t>1.42835524742159</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>1.3671354147369</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>159.58</t>
+          <t>1.59580142761857</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>1.10813826777662</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>80.29</t>
+          <t>1.05170801065284</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>0.982875677250779</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>0.80715977758995</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>48.43</t>
+          <t>0.688489212115273</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>0.703719748519215</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>45.39</t>
+          <t>0.661454875067071</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>55.77</t>
+          <t>0.772117131646088</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>0.775043451977198</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>67.08</t>
+          <t>0.929615745332139</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>0.998706817507294</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>70.46</t>
+          <t>0.964728022519207</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>1.1906900501509</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>1.18352154158265</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>114.15</t>
+          <t>1.14147149692565</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>0.516584504318059</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>34.34</t>
+          <t>0.575789231740001</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>0.634406208508538</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>0.588491577844775</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>0.534342302434744</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>0.546552711172193</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>0.610860464931189</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>0.833515131709342</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>0.88713159917232</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>59.31</t>
+          <t>0.948132192491363</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>65.65</t>
+          <t>1.02604983501998</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>51.18</t>
+          <t>0.863763448760398</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>0.939833593179595</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>68.05</t>
+          <t>1.04192534082257</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>104.09</t>
+          <t>1.04094349140241</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>77.77</t>
+          <t>1.01557995920163</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>72.29</t>
+          <t>0.947002219541328</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>66.59</t>
+          <t>0.887022497598293</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>0.802441122623448</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>57.61</t>
+          <t>0.787792519969558</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>56.85</t>
+          <t>0.800841479584786</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>0.793627397476243</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>0.872418344678817</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>69.64</t>
+          <t>0.944499656343326</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>1.0930553839345</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>84.63</t>
+          <t>1.1030154521469</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>77.12</t>
+          <t>1.04001727165519</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>69.04</t>
+          <t>0.943861769984945</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>0.883515194492019</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>86.15</t>
+          <t>0.861453792068475</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>145.29</t>
+          <t>1.81031962788905</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>137.45</t>
+          <t>1.67513187746815</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>125.13</t>
+          <t>1.53644799211462</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>1.33088908715775</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>138.38</t>
+          <t>1.66944034926033</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>136.69</t>
+          <t>1.65786708606392</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>110.27</t>
+          <t>1.35508088337987</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>135.67</t>
+          <t>1.62311830057982</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>128.41</t>
+          <t>1.54645740391753</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>148.43</t>
+          <t>1.83531016142203</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>193.47</t>
+          <t>2.32087476706974</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>163.75</t>
+          <t>1.970408329614</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>171.11</t>
+          <t>2.05485046801905</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>1.77727358835712</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>160.52</t>
+          <t>1.60523668280187</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>0.74786550923327</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>0.750838902165941</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>43.49</t>
+          <t>0.661719737533796</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>0.606632948978374</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>0.527839284588881</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>0.439749787387243</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>0.380153020245008</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>0.546498432114973</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>0.222369609150143</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>0.0818225509957582</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>0.117023648533223</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>0.0910113517755289</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>0.20807056886077</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.215768638927101</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>0.160914582989073</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>166.17</t>
+          <t>2.05736565070805</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>167.54</t>
+          <t>2.00768922209023</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>174.86</t>
+          <t>2.05935460620978</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>160.52</t>
+          <t>1.90825736027917</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>164.33</t>
+          <t>1.94072375645867</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>161.41</t>
+          <t>1.92868763001317</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>136.74</t>
+          <t>1.65835245028187</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>121.59</t>
+          <t>1.4941046040346</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>136.14</t>
+          <t>1.66599274867695</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>171.44</t>
+          <t>2.10650415500662</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>225.78</t>
+          <t>2.71810475894836</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>217.15</t>
+          <t>2.62644665554579</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>219.24</t>
+          <t>2.64802210131349</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>220.6</t>
+          <t>2.64573237095511</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>231.53</t>
+          <t>2.31529075495176</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>312.38</t>
+          <t>3.50090603322931</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>278.56</t>
+          <t>3.13782976772696</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>263.34</t>
+          <t>2.9823006853922</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>295.64</t>
+          <t>3.32252616616859</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>324.39</t>
+          <t>3.61364809546145</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>325.94</t>
+          <t>3.6397489388587</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>337.82</t>
+          <t>3.7687231588351</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>347.74</t>
+          <t>3.86217793571643</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>371.79</t>
+          <t>4.13663338406492</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>367.85</t>
+          <t>4.09371834968624</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>378.07</t>
+          <t>4.18802776408236</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>387.42</t>
+          <t>4.30882019118309</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>389.56</t>
+          <t>4.30965145892726</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>375.48</t>
+          <t>4.1451341188385</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>419.53</t>
+          <t>4.19531996959987</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>162.17</t>
+          <t>1.98582181802533</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>143.73</t>
+          <t>1.7661752841094</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>139.63</t>
+          <t>1.70133551199752</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>102.91</t>
+          <t>1.31496751840461</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>104.21</t>
+          <t>1.305667416521</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>94.78</t>
+          <t>1.20816582029247</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>99.64</t>
+          <t>1.27282427490878</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>111.59</t>
+          <t>1.3969738720412</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>98.46</t>
+          <t>1.26381421563691</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>108.26</t>
+          <t>1.42840657046848</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>126.32</t>
+          <t>1.61087531845213</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>124.48</t>
+          <t>1.61838931043024</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>120.17</t>
+          <t>1.5706116205942</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>1.568373117573</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>171.54</t>
+          <t>1.71542501791772</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-27.23</t>
+          <t>-0.184553716654435</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-23.18</t>
+          <t>-0.145075231552453</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-26.28</t>
+          <t>-0.173293674192123</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-22.43</t>
+          <t>-0.125922508343612</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>-0.0911426700620951</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-0.0519445832988013</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-16.21</t>
+          <t>-0.0551172910763327</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-0.0742231843887496</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-21.36</t>
+          <t>-0.115767357859113</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>0.000724747003754578</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>0.22410831959236</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>0.251432576249049</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>0.320501431778974</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-0.0778627072074396</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-0.0801412509424582</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>205.42</t>
+          <t>2.27247447717382</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>166.52</t>
+          <t>1.82979969100357</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>196.05</t>
+          <t>2.15663091457488</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>204.96</t>
+          <t>2.25872977104669</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>221.78</t>
+          <t>2.43624836306335</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>225.22</t>
+          <t>2.48751678833516</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>237.25</t>
+          <t>2.63218714284176</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>240.82</t>
+          <t>2.67183095410793</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>216.8</t>
+          <t>2.43341179391244</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>250.35</t>
+          <t>2.80310571905409</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>236.51</t>
+          <t>2.66315134659654</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>232.5</t>
+          <t>2.62851811096224</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>246.28</t>
+          <t>2.77924523223116</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>234.68</t>
+          <t>2.65773106606008</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>264.94</t>
+          <t>2.64935571544101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>97.77</t>
+          <t>1.20252934511377</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>94.99</t>
+          <t>1.15583375858321</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>101.31</t>
+          <t>1.2412163183008</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>93.09</t>
+          <t>1.15737999138412</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>1.13641011901411</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>1.18437607917747</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>105.57</t>
+          <t>1.30490469755893</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>113.3</t>
+          <t>1.38661817300321</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>110.01</t>
+          <t>1.36276840023528</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>127.26</t>
+          <t>1.57349701501196</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>1.69197407990174</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>126.37</t>
+          <t>1.56467842269078</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>132.33</t>
+          <t>1.63649299743089</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>129.55</t>
+          <t>1.59048096634201</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>169.22</t>
+          <t>1.69222267585675</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>59.27</t>
+          <t>0.847698955342534</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>58.03</t>
+          <t>0.833670559171973</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>111.45</t>
+          <t>1.4548615125255</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>99.05</t>
+          <t>1.29466832606176</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>137.03</t>
+          <t>1.69327675868559</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>99.61</t>
+          <t>1.26472085971017</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>103.89</t>
+          <t>1.2949655210384</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>103.03</t>
+          <t>1.2829949773769</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>96.81</t>
+          <t>1.22109855249483</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>108.33</t>
+          <t>1.36433330674263</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>114.6</t>
+          <t>1.39282589765794</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>146.4</t>
+          <t>1.75939149228281</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>210.85</t>
+          <t>2.53418811834056</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>227.18</t>
+          <t>2.71743546946412</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>257.4</t>
+          <t>2.57403616893056</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>155.14</t>
+          <t>1.76278079973677</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>152.31</t>
+          <t>1.7255341308407</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>141.49</t>
+          <t>1.62796667853398</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>122.34</t>
+          <t>1.4317958004909</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>112.03</t>
+          <t>1.2682727227792</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>106.92</t>
+          <t>1.25174328699907</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>105.59</t>
+          <t>1.23585769460319</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>1.04044695621064</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>89.08</t>
+          <t>1.04059116480306</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>80.64</t>
+          <t>0.948789488309119</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>0.80965058740127</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>0.835277997622197</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>56.33</t>
+          <t>0.694224872071258</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>0.656623144471963</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>0.901977318263524</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>254.88</t>
+          <t>3.21563395587499</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>272.14</t>
+          <t>3.43803168894085</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>253.87</t>
+          <t>3.22194276361238</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>228.38</t>
+          <t>2.91567647133876</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>171.36</t>
+          <t>2.18498116185981</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>164.53</t>
+          <t>2.13457642802836</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>144.15</t>
+          <t>1.87829483883678</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>109.04</t>
+          <t>1.42592187674232</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>123.72</t>
+          <t>1.6173645110885</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>94.17</t>
+          <t>1.29130603799949</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>126.11</t>
+          <t>1.67707108929112</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>121.18</t>
+          <t>1.63791282993604</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>107.11</t>
+          <t>1.4379909347671</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>1.28191076870233</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>128.24</t>
+          <t>1.2823780791567</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>0.843166448774272</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>0.807796870977405</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>0.872262219763655</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>0.687416237537225</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>0.467758055312561</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>0.400501278754205</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>22.43</t>
+          <t>0.380653836340519</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>0.405593759521509</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>0.414810940952832</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>0.403226715272464</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>0.507750138326163</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>0.415460492638477</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>0.445394868978702</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>27.77</t>
+          <t>0.448233981111871</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>0.447853625650255</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>59.86</t>
+          <t>0.830532286874724</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>0.844142134793813</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>0.785436886450699</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>0.664333779479509</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>0.572950862560858</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>0.623022123497064</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>43.89</t>
+          <t>0.654736618837415</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>0.707317501108845</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>0.746384243645573</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>0.880608044007368</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>81.39</t>
+          <t>1.104383921162</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>63.87</t>
+          <t>0.898261305754209</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>74.41</t>
+          <t>1.02939098403172</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>0.915899461781607</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>95.24</t>
+          <t>0.952411484300255</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>170.02</t>
+          <t>1.95812991244593</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>172.79</t>
+          <t>1.95397761346094</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>203.21</t>
+          <t>2.27482671745718</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>195.28</t>
+          <t>2.20599083480597</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>177.05</t>
+          <t>2.02358145845862</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>203.1</t>
+          <t>2.35247668848008</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>215.4</t>
+          <t>2.52292677964147</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>2.52524461039474</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>220.42</t>
+          <t>2.64076146393069</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>238.12</t>
+          <t>2.89164000264548</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>222.96</t>
+          <t>2.65952756133556</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>213.59</t>
+          <t>2.54544005810335</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>2.75755345283449</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>254.34</t>
+          <t>2.99330640674049</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>315.35</t>
+          <t>3.15352078039902</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>0.409884894447838</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>0.359002970060208</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>0.305041614547547</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.302912454099922</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>0.336447976338599</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>0.359167110477873</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>0.4019013413848</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>0.491464222385441</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>0.570634040839145</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>0.59639570250563</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>44.48</t>
+          <t>0.612486002696638</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>0.639179357438276</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>0.697443156584424</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>59.55</t>
+          <t>0.798787924409999</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>0.702329322415584</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>55.38</t>
+          <t>0.759567282576884</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>51.75</t>
+          <t>0.711714942424758</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>45.71</t>
+          <t>0.64904449179993</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>0.600946660417283</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>0.589901534982531</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>0.590396242511964</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>44.04</t>
+          <t>0.644502352677883</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>56.08</t>
+          <t>0.777869721377101</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>0.901904133094757</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>0.980776249831617</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>77.66</t>
+          <t>1.05285435828218</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>77.62</t>
+          <t>1.06331144637876</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>1.06159534051403</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>83.98</t>
+          <t>1.1064378447166</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>110.77</t>
+          <t>1.10774923210872</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.0778881517920325</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.103410358683548</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>0.0897226775859319</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.122268381627022</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>0.196831377619591</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>0.187860374858797</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>0.194316210519922</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>0.268458852391483</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>0.304565555749587</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>0.309003280189478</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>0.378178652110582</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>0.468225617706861</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>0.477942140380787</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>0.509766123525361</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>0.538556116959603</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>0.49253979648622</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>0.514742131098094</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>0.504752017102118</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>0.525792285321945</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>0.570489046429276</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>0.590744723974158</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>45.12</t>
+          <t>0.600850730571303</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>53.52</t>
+          <t>0.678687899090342</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>54.71</t>
+          <t>0.697199129575401</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>0.695306843530323</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>60.02</t>
+          <t>0.755648259600644</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>0.798551398281752</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>64.59</t>
+          <t>0.811698024094852</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>69.93</t>
+          <t>0.859531665381508</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>0.900815720813803</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>127.05</t>
+          <t>1.51686435727401</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>137.31</t>
+          <t>1.62992465870534</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>118.03</t>
+          <t>1.42772131214252</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>119.82</t>
+          <t>1.44703583262955</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>102.69</t>
+          <t>1.25346208208349</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>101.39</t>
+          <t>1.24093191568717</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>95.85</t>
+          <t>1.18498698716163</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>1.11389579815042</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>84.78</t>
+          <t>1.0594282035362</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>95.84</t>
+          <t>1.20415251175565</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>105.51</t>
+          <t>1.31125240558504</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>109.37</t>
+          <t>1.35910487359866</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>121.22</t>
+          <t>1.49385471707891</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>139.45</t>
+          <t>1.70675882245062</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>198.51</t>
+          <t>1.98511578931502</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>0.471338123209078</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>0.494580312221404</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>0.471629830574853</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>0.382951861615207</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>0.461769278063739</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>0.479376714540383</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>0.492898429635505</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>0.575159631663686</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>0.54279387259094</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>0.623178533050264</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>36.94</t>
+          <t>0.60691760968683</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>0.488550411419507</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>0.523543497746634</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>0.433557927183905</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>44.64</t>
+          <t>0.446410523722199</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>0.306656704254681</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>0.215713331687883</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.150943499348929</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>0.105663306136503</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>0.0332611364420168</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>0.0615864371823698</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>0.0495426729491852</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>0.0488434609204462</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>0.0792646806624895</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>0.111345917520548</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.227886155276603</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>0.120396997567825</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>0.224005173636684</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>0.101575484849561</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>0.0997856961020864</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
